--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487050_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487050_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0845</v>
+        <v>6.4692</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8588</v>
+        <v>6.538</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2257</v>
+        <v>-0.0688</v>
       </c>
       <c r="G2" t="n">
         <v>4.8722</v>
@@ -610,13 +610,13 @@
         <v>2.3161</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5175</v>
+        <v>0.9022</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4349</v>
+        <v>0.2443</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9524</v>
+        <v>0.658</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6562</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. CAMPBELL</t>
+          <t>G. TSULAIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3226</v>
+        <v>2.0816</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5929</v>
+        <v>4.7942</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2704</v>
+        <v>-2.7126</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0466</v>
+        <v>-0.8372000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7757</v>
+        <v>0.6044</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.729</v>
+        <v>-1.4416</v>
       </c>
       <c r="J3" t="n">
-        <v>5.8898</v>
+        <v>2.5332</v>
       </c>
       <c r="K3" t="n">
-        <v>5.6456</v>
+        <v>2.7216</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2442</v>
+        <v>-0.1884</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.8432</v>
+        <v>-3.3704</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.87</v>
+        <v>-2.1172</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9732</v>
+        <v>-1.2531</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.5091</v>
+        <v>-0.772</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.8602</v>
+        <v>-2.8951</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3511</v>
+        <v>2.1231</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4992</v>
+        <v>0.2928</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9915</v>
+        <v>0.2443</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5076</v>
+        <v>0.0485</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2859</v>
+        <v>3.398</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5717</v>
+        <v>4.9119</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2859</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. TSULAIA</t>
+          <t>S. CAMPBELL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7927</v>
+        <v>1.8453</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1745</v>
+        <v>2.892</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.3818</v>
+        <v>-1.0467</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8372000000000001</v>
+        <v>3.0466</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6044</v>
+        <v>3.7757</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.4416</v>
+        <v>-0.729</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5332</v>
+        <v>5.8898</v>
       </c>
       <c r="K4" t="n">
-        <v>2.7216</v>
+        <v>5.6456</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1884</v>
+        <v>0.2442</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.3704</v>
+        <v>-2.8432</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.1172</v>
+        <v>-1.87</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2531</v>
+        <v>-0.9732</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.772</v>
+        <v>-2.5091</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.8951</v>
+        <v>-3.8602</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1231</v>
+        <v>1.3511</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9961</v>
+        <v>1.0219</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3754</v>
+        <v>0.2905</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6207</v>
+        <v>0.7313</v>
       </c>
       <c r="V4" t="n">
-        <v>3.398</v>
+        <v>0.2859</v>
       </c>
       <c r="W4" t="n">
-        <v>4.9119</v>
+        <v>0.5717</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.5138</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1827</v>
+        <v>-0.9557</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7866</v>
+        <v>-0.5863</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3961</v>
+        <v>-0.3694</v>
       </c>
       <c r="G5" t="n">
         <v>-1.0816</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1011</v>
+        <v>0.1259</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.119</v>
+        <v>0.0813</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.5154</v>
+        <v>-2.0379</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6037</v>
+        <v>-1.1262</v>
       </c>
       <c r="F6" t="n">
         <v>-0.9118000000000001</v>
@@ -922,10 +922,10 @@
         <v>1.158</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9637</v>
+        <v>0.4412</v>
       </c>
       <c r="T6" t="n">
-        <v>1.125</v>
+        <v>0.6025</v>
       </c>
       <c r="U6" t="n">
         <v>-0.1613</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. MERKVILADZE</t>
+          <t>A. AREVALO NEGUERUELA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.7955</v>
+        <v>-2.9189</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.4975</v>
+        <v>-2.8046</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.298</v>
+        <v>-0.1143</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.7895</v>
+        <v>-0.9858</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8145</v>
+        <v>-0.828</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.975</v>
+        <v>-0.1578</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.9621</v>
+        <v>-0.1781</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6676</v>
+        <v>-0.3002</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2945</v>
+        <v>0.1221</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8274</v>
+        <v>-0.8076</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1469</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6805</v>
+        <v>-0.2799</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.772</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R7" t="n">
-        <v>0.193</v>
+        <v>0.965</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7661</v>
+        <v>0.2406</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4297</v>
+        <v>0.2687</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3364</v>
+        <v>-0.0281</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.2436</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2436</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. AREVALO NEGUERUELA</t>
+          <t>D. MERKVILADZE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.5316</v>
+        <v>-3.2238</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.2834</v>
+        <v>-2.7384</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2482</v>
+        <v>-0.4854</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9858</v>
+        <v>-2.7895</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.828</v>
+        <v>-0.8145</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1578</v>
+        <v>-1.975</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1781</v>
+        <v>-1.9621</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3002</v>
+        <v>-0.6676</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1221</v>
+        <v>-1.2945</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8076</v>
+        <v>-0.8274</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5276999999999999</v>
+        <v>-0.1469</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2799</v>
+        <v>-0.6805</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.9301</v>
+        <v>-0.772</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R8" t="n">
-        <v>0.965</v>
+        <v>0.193</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3721</v>
+        <v>0.3378</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2102</v>
+        <v>0.1887</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.162</v>
+        <v>0.149</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2436</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2436</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5741</v>
+        <v>-3.3332</v>
       </c>
       <c r="E9" t="n">
         <v>-1.8374</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7367</v>
+        <v>-1.4958</v>
       </c>
       <c r="G9" t="n">
         <v>-3.5797</v>
@@ -1156,13 +1156,13 @@
         <v>1.3511</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1368</v>
+        <v>0.1041</v>
       </c>
       <c r="T9" t="n">
         <v>0.0265</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1633</v>
+        <v>0.0776</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2436</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.3473</v>
+        <v>-4.7812</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.8918</v>
+        <v>-4.5131</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4555</v>
+        <v>-0.2681</v>
       </c>
       <c r="G10" t="n">
         <v>-5.3678</v>
@@ -1234,13 +1234,13 @@
         <v>2.1231</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1725</v>
+        <v>0.3936</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1969</v>
+        <v>0.1818</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0244</v>
+        <v>0.2118</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.746800000000001</v>
+        <v>-6.854600000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2742000000000004</v>
+        <v>0.6181999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-7.4728</v>
+        <v>-7.472899999999999</v>
       </c>
       <c r="G11" t="n">
         <v>-8.780999999999999</v>
@@ -1285,13 +1285,13 @@
         <v>-5.9763</v>
       </c>
       <c r="J11" t="n">
-        <v>9.473200000000002</v>
+        <v>9.473199999999999</v>
       </c>
       <c r="K11" t="n">
         <v>9.184000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2894000000000001</v>
+        <v>0.289400000000001</v>
       </c>
       <c r="M11" t="n">
         <v>-18.2541</v>
@@ -1300,7 +1300,7 @@
         <v>-11.9884</v>
       </c>
       <c r="O11" t="n">
-        <v>-6.265700000000001</v>
+        <v>-6.2657</v>
       </c>
       <c r="P11" t="n">
         <v>-3.860100000000001</v>
@@ -1312,13 +1312,13 @@
         <v>11.5805</v>
       </c>
       <c r="S11" t="n">
-        <v>2.9679</v>
+        <v>3.860100000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2363</v>
+        <v>2.1286</v>
       </c>
       <c r="U11" t="n">
-        <v>1.7313</v>
+        <v>1.7314</v>
       </c>
       <c r="V11" t="n">
         <v>1.9265</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.1101</v>
+        <v>4.8448</v>
       </c>
       <c r="E12" t="n">
-        <v>4.611</v>
+        <v>5.2118</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5009</v>
+        <v>-0.367</v>
       </c>
       <c r="G12" t="n">
         <v>5.8108</v>
@@ -1390,13 +1390,13 @@
         <v>2.7021</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6478</v>
+        <v>-0.9132</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4436</v>
+        <v>-0.8427</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2043</v>
+        <v>-0.0704</v>
       </c>
       <c r="V12" t="n">
         <v>1.1052</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.3725</v>
+        <v>3.4528</v>
       </c>
       <c r="E13" t="n">
         <v>4.9096</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5371</v>
+        <v>-1.4568</v>
       </c>
       <c r="G13" t="n">
         <v>4.3186</v>
@@ -1468,13 +1468,13 @@
         <v>2.5091</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5255</v>
+        <v>-0.4452</v>
       </c>
       <c r="T13" t="n">
         <v>-0.3595</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1659</v>
+        <v>-0.0856</v>
       </c>
       <c r="V13" t="n">
         <v>-1.9647</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. DIEYE</t>
+          <t>J. DOSS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7143</v>
+        <v>2.9605</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2438</v>
+        <v>2.9067</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5294</v>
+        <v>0.0538</v>
       </c>
       <c r="G14" t="n">
-        <v>2.8044</v>
+        <v>1.7933</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5273</v>
+        <v>2.9329</v>
       </c>
       <c r="I14" t="n">
-        <v>0.277</v>
+        <v>-1.1396</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1059</v>
+        <v>3.3008</v>
       </c>
       <c r="K14" t="n">
-        <v>3.9431</v>
+        <v>3.8548</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1628</v>
+        <v>-0.5541</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3015</v>
+        <v>-1.5074</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.4157</v>
+        <v>-0.9219000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1142</v>
+        <v>-0.5855</v>
       </c>
       <c r="P14" t="n">
-        <v>1.158</v>
+        <v>-0.386</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R14" t="n">
-        <v>1.158</v>
+        <v>1.5441</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2637</v>
+        <v>-0.4941</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4918</v>
+        <v>0.0222</v>
       </c>
       <c r="U14" t="n">
-        <v>0.228</v>
+        <v>-0.5163</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.9843</v>
+        <v>2.0473</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3704</v>
+        <v>1.5138</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.614</v>
+        <v>0.5334</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. DOSS</t>
+          <t>A. DIEYE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6456</v>
+        <v>2.874</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2071</v>
+        <v>3.6443</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5616</v>
+        <v>-0.7704</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7933</v>
+        <v>2.8044</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9329</v>
+        <v>2.5273</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.1396</v>
+        <v>0.277</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3008</v>
+        <v>4.1059</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8548</v>
+        <v>3.9431</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5541</v>
+        <v>0.1628</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5074</v>
+        <v>-1.3015</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9219000000000001</v>
+        <v>-1.4157</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5855</v>
+        <v>0.1142</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.386</v>
+        <v>1.158</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5441</v>
+        <v>1.158</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8090000000000001</v>
+        <v>-0.1041</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3226</v>
+        <v>-0.0912</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1316</v>
+        <v>-0.0129</v>
       </c>
       <c r="V15" t="n">
-        <v>2.0473</v>
+        <v>-0.9843</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5138</v>
+        <v>-0.3704</v>
       </c>
       <c r="X15" t="n">
-        <v>0.5334</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2077</v>
+        <v>1.9292</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7242</v>
+        <v>2.1248</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5165</v>
+        <v>-0.1956</v>
       </c>
       <c r="G16" t="n">
         <v>1.5242</v>
@@ -1702,13 +1702,13 @@
         <v>1.7371</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8256</v>
+        <v>-0.1041</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5658</v>
+        <v>-0.1652</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2598</v>
+        <v>0.0611</v>
       </c>
       <c r="V16" t="n">
         <v>-1.228</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. DIEYE</t>
+          <t>S. LOPEZ RAMOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3938</v>
+        <v>0.4111</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6555</v>
+        <v>-0.5837</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0494</v>
+        <v>0.9948</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6768</v>
+        <v>0.0621</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2451</v>
+        <v>0.4627</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5684</v>
+        <v>-0.4006</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.8586</v>
+        <v>-0.6055</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.8993</v>
+        <v>0.0621</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0407</v>
+        <v>-0.6676</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1818</v>
+        <v>0.6676</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6542</v>
+        <v>0.4006</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.267</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3511</v>
+        <v>0.386</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3511</v>
+        <v>0.386</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6617</v>
+        <v>-0.037</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8593</v>
+        <v>0.0218</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1977</v>
+        <v>-0.0588</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9421</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. LOPEZ RAMOS</t>
+          <t>M. DIEYE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2644</v>
+        <v>-0.1935</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.784</v>
+        <v>-2.4567</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0483</v>
+        <v>2.2632</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0621</v>
+        <v>-0.6768</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4627</v>
+        <v>-1.2451</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4006</v>
+        <v>0.5684</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6055</v>
+        <v>-1.8586</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0621</v>
+        <v>-1.8993</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6676</v>
+        <v>0.0407</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6676</v>
+        <v>1.1818</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4006</v>
+        <v>0.6542</v>
       </c>
       <c r="O18" t="n">
-        <v>0.267</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>0.386</v>
+        <v>1.3511</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.386</v>
+        <v>1.3511</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1838</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1785</v>
+        <v>0.0582</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0053</v>
+        <v>0.0162</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.9421</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. DINIS</t>
+          <t>A. MARCOS SÁNCHEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0772</v>
+        <v>-0.2908</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5281</v>
+        <v>-0.3282</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.0374</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0096</v>
+        <v>-0.3989</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0475</v>
+        <v>0.4151</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0378</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6587</v>
+        <v>-0.2122</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4552</v>
+        <v>0.4554</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2035</v>
+        <v>-0.6676</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6683</v>
+        <v>-0.1866</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5026</v>
+        <v>-0.0403</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1657</v>
+        <v>-0.1464</v>
       </c>
       <c r="P19" t="n">
-        <v>-0</v>
+        <v>0.386</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9301</v>
+        <v>0.386</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2096</v>
+        <v>-0.278</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4574</v>
+        <v>-0.116</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7522</v>
+        <v>-0.162</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1228</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.4087</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. MARCOS SÁNCHEZ</t>
+          <t>A. DINIS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7783</v>
+        <v>-1.0055</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6286</v>
+        <v>-1.129</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1496</v>
+        <v>0.1234</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3989</v>
+        <v>-1.0096</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4151</v>
+        <v>-1.0475</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8139999999999999</v>
+        <v>0.0378</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2122</v>
+        <v>0.6587</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4554</v>
+        <v>0.4552</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6676</v>
+        <v>0.2035</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1866</v>
+        <v>-1.6683</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0403</v>
+        <v>-1.5026</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1464</v>
+        <v>-0.1657</v>
       </c>
       <c r="P20" t="n">
-        <v>0.386</v>
+        <v>-0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R20" t="n">
-        <v>0.386</v>
+        <v>1.9301</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7654</v>
+        <v>0.1269</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4164</v>
+        <v>-0.1434</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.349</v>
+        <v>0.2703</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.1228</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.4087</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8616</v>
+        <v>-2.6616</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4984</v>
+        <v>-2.2982</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3631</v>
+        <v>-0.3635</v>
       </c>
       <c r="G21" t="n">
         <v>-1.8377</v>
@@ -2092,13 +2092,13 @@
         <v>0.193</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2518</v>
+        <v>-0.0519</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3424</v>
+        <v>-0.1421</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0905</v>
+        <v>0.0902</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3989</v>
+        <v>-3.9065</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.1283</v>
+        <v>-4.5289</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7294</v>
+        <v>0.6224</v>
       </c>
       <c r="G22" t="n">
         <v>-3.6095</v>
@@ -2170,13 +2170,13 @@
         <v>1.5441</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4336</v>
+        <v>-0.074</v>
       </c>
       <c r="T22" t="n">
-        <v>0.427</v>
+        <v>0.0265</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0066</v>
+        <v>-0.1005</v>
       </c>
       <c r="V22" t="n">
         <v>0.1631</v>
@@ -2203,22 +2203,22 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>7.746799999999999</v>
+        <v>8.4145</v>
       </c>
       <c r="E23" t="n">
-        <v>7.472799999999999</v>
+        <v>7.472500000000004</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2742000000000002</v>
+        <v>0.9416999999999995</v>
       </c>
       <c r="G23" t="n">
-        <v>8.780900000000001</v>
+        <v>8.780899999999999</v>
       </c>
       <c r="H23" t="n">
         <v>2.8046</v>
       </c>
       <c r="I23" t="n">
-        <v>5.9762</v>
+        <v>5.976199999999999</v>
       </c>
       <c r="J23" t="n">
         <v>18.2543</v>
@@ -2227,7 +2227,7 @@
         <v>11.9885</v>
       </c>
       <c r="L23" t="n">
-        <v>6.265700000000001</v>
+        <v>6.265700000000002</v>
       </c>
       <c r="M23" t="n">
         <v>-9.4732</v>
@@ -2239,7 +2239,7 @@
         <v>-0.2893</v>
       </c>
       <c r="P23" t="n">
-        <v>3.860300000000001</v>
+        <v>3.8603</v>
       </c>
       <c r="Q23" t="n">
         <v>-11.5805</v>
@@ -2248,13 +2248,13 @@
         <v>15.4407</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.9677</v>
+        <v>-2.3003</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.7317</v>
+        <v>-1.7314</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2363</v>
+        <v>-0.5687</v>
       </c>
       <c r="V23" t="n">
         <v>-1.9263</v>
@@ -2263,7 +2263,7 @@
         <v>2.5306</v>
       </c>
       <c r="X23" t="n">
-        <v>-4.4571</v>
+        <v>-4.457099999999999</v>
       </c>
     </row>
   </sheetData>
